--- a/PORTAL IQ.xlsx
+++ b/PORTAL IQ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elcio.nunes\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503955E5-4A17-4DC0-9B0E-3292A23F4304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73451191-FF06-42FE-878F-EAB431009AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{897EA0BA-11DF-40E6-8E49-799C2344DF81}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_IQ" sheetId="1" r:id="rId1"/>
     <sheet name="Base_Tecnicos" sheetId="2" r:id="rId2"/>
-    <sheet name="CERTIFICADOS" sheetId="3" r:id="rId3"/>
+    <sheet name="Certificados" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294964356" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294965850" uniqueCount="189">
   <si>
     <t>re_iq</t>
   </si>
@@ -888,114 +888,6 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1049,6 +941,84 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1058,134 +1028,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1220,6 +1070,26 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1398,6 +1268,136 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1412,31 +1412,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}" name="Tabela2" displayName="Tabela2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="20" headerRowBorderDxfId="25" tableBorderDxfId="26" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}" name="Tabela2" displayName="Tabela2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="A1:D14" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2A20E4A5-AF55-44E6-A4E2-B2D793288803}" name="re_iq" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{23EBEA0A-D98A-4536-AA12-E2AF914499ED}" name="senha" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{19B128AC-4E26-4DAE-9B5C-780E4F95DAB9}" name="nome_iq" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{C1A886F2-0489-4ABD-9F84-D9ECBC1ED5F6}" name="PERFIL" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{2A20E4A5-AF55-44E6-A4E2-B2D793288803}" name="re_iq" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{23EBEA0A-D98A-4536-AA12-E2AF914499ED}" name="senha" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{19B128AC-4E26-4DAE-9B5C-780E4F95DAB9}" name="nome_iq" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{C1A886F2-0489-4ABD-9F84-D9ECBC1ED5F6}" name="PERFIL" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2125BA19-808D-4B8F-BDC5-306E46DE35D9}" name="Tabela1" displayName="Tabela1" ref="A1:G72" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2125BA19-808D-4B8F-BDC5-306E46DE35D9}" name="Tabela1" displayName="Tabela1" ref="A1:G72" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AE302A53-063D-4D0E-B6D7-ADD29FD4D6B5}" name="re" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{DE145AF2-8CC2-4F13-81B6-1888D59ADAE1}" name="login" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{EA70B00C-C817-4FDA-B4F7-1C2B651EC4C8}" name="nome" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{123CE67E-6737-40DE-B649-26C14CF5783C}" name="status_certificacao" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{AE302A53-063D-4D0E-B6D7-ADD29FD4D6B5}" name="re" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{DE145AF2-8CC2-4F13-81B6-1888D59ADAE1}" name="login" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{EA70B00C-C817-4FDA-B4F7-1C2B651EC4C8}" name="nome" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{123CE67E-6737-40DE-B649-26C14CF5783C}" name="status_certificacao" dataDxfId="20">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{92C55EB9-51B4-43CF-B1CD-7D160F1F6E71}" name="regiao" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{B66CA9F0-2091-4C72-8861-DFD2AB54E130}" name="re_iq_responsavel" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{B545E271-6657-484A-B9B0-961D99B609F4}" name="Acompanhamento" dataDxfId="0">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{92C55EB9-51B4-43CF-B1CD-7D160F1F6E71}" name="regiao" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{B66CA9F0-2091-4C72-8861-DFD2AB54E130}" name="re_iq_responsavel" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{B545E271-6657-484A-B9B0-961D99B609F4}" name="Acompanhamento" dataDxfId="17">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1444,33 +1444,33 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}" name="Tabela3" displayName="Tabela3" ref="A1:B63" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}" name="Tabela3" displayName="Tabela3" ref="A1:B63" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="A1:B63" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}"/>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{42330779-A1A8-47D6-9BED-9B7E341EF2F7}" name="LOGIN" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{FDA0CAEF-1181-4A76-BE79-5A6EB75F17EA}" name="CERTIFICADO JULHO" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{42330779-A1A8-47D6-9BED-9B7E341EF2F7}" name="LOGIN" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{FDA0CAEF-1181-4A76-BE79-5A6EB75F17EA}" name="CERTIFICADO JULHO" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}" name="Tabela4" displayName="Tabela4" ref="D1:E67" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}" name="Tabela4" displayName="Tabela4" ref="D1:E67" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="D1:E67" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{CFB25483-5D14-4A06-9A44-C6208CAE627A}" name="LOGIN"/>
-    <tableColumn id="2" xr3:uid="{BBEDB3EF-662A-4CA6-9436-5C5A44A68C83}" name="CERTIFICADO AGOSTO" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{BBEDB3EF-662A-4CA6-9436-5C5A44A68C83}" name="CERTIFICADO AGOSTO" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}" name="Tabela5" displayName="Tabela5" ref="G1:H74" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}" name="Tabela5" displayName="Tabela5" ref="G1:H74" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="G1:H74" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5CB42125-2587-4C90-9CDA-BAD40E0C4647}" name="LOGIN"/>
-    <tableColumn id="2" xr3:uid="{7DFAC3F2-BD84-4FD7-A8B1-F7034CD0D422}" name="CERTIFICADO SETEMBRO" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7DFAC3F2-BD84-4FD7-A8B1-F7034CD0D422}" name="CERTIFICADO SETEMBRO" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2065,7 +2065,7 @@
         <v>5996</v>
       </c>
       <c r="G2" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
         <v>5996</v>
       </c>
       <c r="G3" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         <v>5996</v>
       </c>
       <c r="G4" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
         <v>6540</v>
       </c>
       <c r="G5" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         <v>6540</v>
       </c>
       <c r="G6" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>4045</v>
       </c>
       <c r="G7" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         <v>4045</v>
       </c>
       <c r="G8" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
         <v>4045</v>
       </c>
       <c r="G9" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         <v>4045</v>
       </c>
       <c r="G10" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
         <v>5996</v>
       </c>
       <c r="G11" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>4045</v>
       </c>
       <c r="G12" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
         <v>6540</v>
       </c>
       <c r="G13" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
         <v>5996</v>
       </c>
       <c r="G14" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>6540</v>
       </c>
       <c r="G15" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
         <v>4045</v>
       </c>
       <c r="G16" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
         <v>4045</v>
       </c>
       <c r="G17" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
         <v>6540</v>
       </c>
       <c r="G18" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
         <v>5996</v>
       </c>
       <c r="G19" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>4045</v>
       </c>
       <c r="G20" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
         <v>4045</v>
       </c>
       <c r="G21" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
         <v>6540</v>
       </c>
       <c r="G22" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
         <v>6540</v>
       </c>
       <c r="G23" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
         <v>5996</v>
       </c>
       <c r="G24" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>5996</v>
       </c>
       <c r="G25" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
         <v>6540</v>
       </c>
       <c r="G26" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>4045</v>
       </c>
       <c r="G27" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4045</v>
       </c>
       <c r="G28" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
         <v>6540</v>
       </c>
       <c r="G29" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
         <v>5996</v>
       </c>
       <c r="G30" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         <v>6540</v>
       </c>
       <c r="G31" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
         <v>5996</v>
       </c>
       <c r="G32" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
         <v>4045</v>
       </c>
       <c r="G33" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
         <v>6540</v>
       </c>
       <c r="G34" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
         <v>4045</v>
       </c>
       <c r="G35" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>5996</v>
       </c>
       <c r="G36" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         <v>5996</v>
       </c>
       <c r="G37" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
         <v>5996</v>
       </c>
       <c r="G38" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         <v>5996</v>
       </c>
       <c r="G39" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
         <v>4045</v>
       </c>
       <c r="G40" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
         <v>5996</v>
       </c>
       <c r="G41" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
         <v>4045</v>
       </c>
       <c r="G42" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         <v>6540</v>
       </c>
       <c r="G43" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         <v>6540</v>
       </c>
       <c r="G44" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
         <v>6540</v>
       </c>
       <c r="G45" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         <v>6540</v>
       </c>
       <c r="G46" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
         <v>6540</v>
       </c>
       <c r="G47" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
         <v>5996</v>
       </c>
       <c r="G48" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
         <v>5996</v>
       </c>
       <c r="G49" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         <v>4045</v>
       </c>
       <c r="G50" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
         <v>4045</v>
       </c>
       <c r="G51" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         <v>4045</v>
       </c>
       <c r="G52" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
         <v>5996</v>
       </c>
       <c r="G53" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
         <v>5996</v>
       </c>
       <c r="G54" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
         <v>4045</v>
       </c>
       <c r="G55" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>6540</v>
       </c>
       <c r="G56" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         <v>6540</v>
       </c>
       <c r="G57" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
         <v>5996</v>
       </c>
       <c r="G58" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
         <v>5996</v>
       </c>
       <c r="G59" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>4045</v>
       </c>
       <c r="G60" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
         <v>4045</v>
       </c>
       <c r="G61" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
         <v>4045</v>
       </c>
       <c r="G62" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
         <v>6540</v>
       </c>
       <c r="G63" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
         <v>6540</v>
       </c>
       <c r="G64" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
         <v>6540</v>
       </c>
       <c r="G65" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
         <v>5996</v>
       </c>
       <c r="G66" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
         <v>5996</v>
       </c>
       <c r="G67" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
         <v>4045</v>
       </c>
       <c r="G68" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Não</v>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>5996</v>
       </c>
       <c r="G69" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         <v>6540</v>
       </c>
       <c r="G70" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
         <v>4045</v>
       </c>
       <c r="G71" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -3815,23 +3815,23 @@
         <v>5996</v>
       </c>
       <c r="G72" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],CERTIFICADOS!A:B,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>Sim</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A8">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B72">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B70">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">

--- a/PORTAL IQ.xlsx
+++ b/PORTAL IQ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elcio.nunes\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73451191-FF06-42FE-878F-EAB431009AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DE769E-993C-4921-B85D-088006D6728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{897EA0BA-11DF-40E6-8E49-799C2344DF81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{897EA0BA-11DF-40E6-8E49-799C2344DF81}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_IQ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294965850" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294966362" uniqueCount="189">
   <si>
     <t>re_iq</t>
   </si>
@@ -814,38 +814,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -882,11 +859,111 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="33">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1032,213 +1109,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1412,30 +1282,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}" name="Tabela2" displayName="Tabela2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}" name="Tabela2" displayName="Tabela2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="32" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:D14" xr:uid="{43B77F1C-986A-455C-84D0-98802B3F1BC0}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2A20E4A5-AF55-44E6-A4E2-B2D793288803}" name="re_iq" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{23EBEA0A-D98A-4536-AA12-E2AF914499ED}" name="senha" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{19B128AC-4E26-4DAE-9B5C-780E4F95DAB9}" name="nome_iq" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{C1A886F2-0489-4ABD-9F84-D9ECBC1ED5F6}" name="PERFIL" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{2A20E4A5-AF55-44E6-A4E2-B2D793288803}" name="re_iq" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{23EBEA0A-D98A-4536-AA12-E2AF914499ED}" name="senha" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{19B128AC-4E26-4DAE-9B5C-780E4F95DAB9}" name="nome_iq" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{C1A886F2-0489-4ABD-9F84-D9ECBC1ED5F6}" name="PERFIL" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2125BA19-808D-4B8F-BDC5-306E46DE35D9}" name="Tabela1" displayName="Tabela1" ref="A1:G72" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2125BA19-808D-4B8F-BDC5-306E46DE35D9}" name="Tabela1" displayName="Tabela1" ref="A1:G72" totalsRowShown="0" headerRowDxfId="24">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AE302A53-063D-4D0E-B6D7-ADD29FD4D6B5}" name="re" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{DE145AF2-8CC2-4F13-81B6-1888D59ADAE1}" name="login" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{EA70B00C-C817-4FDA-B4F7-1C2B651EC4C8}" name="nome" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{123CE67E-6737-40DE-B649-26C14CF5783C}" name="status_certificacao" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{AE302A53-063D-4D0E-B6D7-ADD29FD4D6B5}" name="re" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{DE145AF2-8CC2-4F13-81B6-1888D59ADAE1}" name="login" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{EA70B00C-C817-4FDA-B4F7-1C2B651EC4C8}" name="nome" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{123CE67E-6737-40DE-B649-26C14CF5783C}" name="status_certificacao" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{92C55EB9-51B4-43CF-B1CD-7D160F1F6E71}" name="regiao" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{B66CA9F0-2091-4C72-8861-DFD2AB54E130}" name="re_iq_responsavel" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{B545E271-6657-484A-B9B0-961D99B609F4}" name="Acompanhamento" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{92C55EB9-51B4-43CF-B1CD-7D160F1F6E71}" name="regiao" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{B66CA9F0-2091-4C72-8861-DFD2AB54E130}" name="re_iq_responsavel" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{B545E271-6657-484A-B9B0-961D99B609F4}" name="Acompanhamento" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1444,33 +1314,33 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}" name="Tabela3" displayName="Tabela3" ref="A1:B63" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}" name="Tabela3" displayName="Tabela3" ref="A1:B63" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:B63" xr:uid="{186284CE-3AAC-4123-B1CA-462A33BA1065}"/>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{42330779-A1A8-47D6-9BED-9B7E341EF2F7}" name="LOGIN" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{FDA0CAEF-1181-4A76-BE79-5A6EB75F17EA}" name="CERTIFICADO JULHO" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{42330779-A1A8-47D6-9BED-9B7E341EF2F7}" name="LOGIN" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{FDA0CAEF-1181-4A76-BE79-5A6EB75F17EA}" name="CERTIFICADO JULHO" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}" name="Tabela4" displayName="Tabela4" ref="D1:E67" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}" name="Tabela4" displayName="Tabela4" ref="D1:E67" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17">
   <autoFilter ref="D1:E67" xr:uid="{EA4F5E4B-CB9E-463A-85DE-B2DA4B83C290}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{CFB25483-5D14-4A06-9A44-C6208CAE627A}" name="LOGIN"/>
-    <tableColumn id="2" xr3:uid="{BBEDB3EF-662A-4CA6-9436-5C5A44A68C83}" name="CERTIFICADO AGOSTO" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BBEDB3EF-662A-4CA6-9436-5C5A44A68C83}" name="CERTIFICADO AGOSTO" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}" name="Tabela5" displayName="Tabela5" ref="G1:H74" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}" name="Tabela5" displayName="Tabela5" ref="G1:H74" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="G1:H74" xr:uid="{67CBFA7C-B0C8-4AE0-A85C-3F5B6B2BB3DE}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5CB42125-2587-4C90-9CDA-BAD40E0C4647}" name="LOGIN"/>
-    <tableColumn id="2" xr3:uid="{7DFAC3F2-BD84-4FD7-A8B1-F7034CD0D422}" name="CERTIFICADO SETEMBRO" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7DFAC3F2-BD84-4FD7-A8B1-F7034CD0D422}" name="CERTIFICADO SETEMBRO" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1797,204 +1667,204 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10" style="3" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="25"/>
+    <col min="4" max="4" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="16">
+      <c r="A2" s="5">
         <v>8433</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>123</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="5">
         <v>5304</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>123</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="5">
         <v>6391</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>123</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="5">
         <v>4045</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>123</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="5">
         <v>5449</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>123</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="5">
         <v>5996</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>123</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="5">
         <v>6540</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>123</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="5">
         <v>2886</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>123</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+      <c r="A10" s="5">
         <v>7563</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>123</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
+      <c r="A11" s="5">
         <v>8017</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
         <v>123</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+      <c r="A12" s="5">
         <v>8502</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>123</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+      <c r="A13" s="5">
         <v>516</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>123</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="8">
         <v>7708</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="4">
         <v>123</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="13" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2014,1824 +1884,1772 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="9" style="5" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="20" t="s">
         <v>171</v>
       </c>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="21">
         <v>8189</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F2" s="16">
+      <c r="E2" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="24">
         <v>5996</v>
       </c>
-      <c r="G2" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G2" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="21">
+        <v>8427</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>8427</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="4" t="str">
+      <c r="E3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
+        <v>8338</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
+        <v>8368</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="16">
+      <c r="E5" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F5" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
+        <v>8496</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>7656</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="21">
+        <v>8337</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
+        <v>8375</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F9" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="21">
+        <v>7704</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="21">
+        <v>8045</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="24">
         <v>5996</v>
       </c>
-      <c r="G3" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Não</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>8338</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G11" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <v>8666</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>8368</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>8496</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G6" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>7656</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="16">
+      <c r="E12" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="24">
         <v>4045</v>
       </c>
-      <c r="G7" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>8337</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G8" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>8375</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G9" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>7704</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G10" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>8045</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F11" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G11" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>8666</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G12" s="5" t="str">
+      <c r="G12" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="21">
         <v>8654</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="4" t="str">
+      <c r="D13" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F13" s="16">
+      <c r="E13" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" s="24">
         <v>6540</v>
       </c>
-      <c r="G13" s="5" t="str">
+      <c r="G13" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="21">
         <v>8213</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F14" s="16">
+      <c r="E14" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14" s="24">
         <v>5996</v>
       </c>
-      <c r="G14" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G14" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="21">
         <v>8585</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="4" t="str">
+      <c r="D15" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="16">
+      <c r="E15" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="24">
         <v>6540</v>
       </c>
-      <c r="G15" s="5" t="str">
+      <c r="G15" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="21">
         <v>8665</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F16" s="16">
+      <c r="E16" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="24">
         <v>4045</v>
       </c>
-      <c r="G16" s="5" t="str">
+      <c r="G16" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="21">
         <v>8589</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="4" t="str">
+      <c r="D17" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" s="16">
+      <c r="E17" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F17" s="24">
         <v>4045</v>
       </c>
-      <c r="G17" s="5" t="str">
+      <c r="G17" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="21">
         <v>7666</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F18" s="16">
+      <c r="E18" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" s="24">
         <v>6540</v>
       </c>
-      <c r="G18" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G18" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="21">
         <v>8594</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="4" t="str">
+      <c r="D19" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="16">
+      <c r="E19" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="24">
         <v>5996</v>
       </c>
-      <c r="G19" s="5" t="str">
+      <c r="G19" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="21">
         <v>8300</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="4" t="str">
+      <c r="D20" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="16">
+      <c r="E20" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F20" s="24">
         <v>4045</v>
       </c>
-      <c r="G20" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G20" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="21">
+        <v>7669</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>7669</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="4" t="str">
+      <c r="E21" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="21">
+        <v>7642</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G21" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>7642</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="16">
+      <c r="E22" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F22" s="24">
         <v>6540</v>
       </c>
-      <c r="G22" s="5" t="str">
+      <c r="G22" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="21">
         <v>2331</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="4" t="str">
+      <c r="D23" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F23" s="16">
+      <c r="E23" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" s="24">
         <v>6540</v>
       </c>
-      <c r="G23" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G23" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="21">
+        <v>5586</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>5586</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F24" s="16">
+      <c r="E24" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="24">
         <v>5996</v>
       </c>
-      <c r="G24" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G24" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="21">
         <v>8058</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="4" t="str">
+      <c r="D25" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F25" s="16">
+      <c r="E25" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F25" s="24">
         <v>5996</v>
       </c>
-      <c r="G25" s="5" t="str">
+      <c r="G25" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="21">
         <v>7533</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F26" s="16">
+      <c r="E26" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="24">
         <v>6540</v>
       </c>
-      <c r="G26" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G26" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="21">
+        <v>8152</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="21">
+        <v>8014</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>8152</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="4" t="str">
+      <c r="E28" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="21">
+        <v>8504</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F27" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G27" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>8014</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F28" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G28" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="E29" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="21">
+        <v>8645</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>8504</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F29" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G29" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>8645</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F30" s="16">
+      <c r="E30" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" s="24">
         <v>5996</v>
       </c>
-      <c r="G30" s="5" t="str">
+      <c r="G30" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="21">
         <v>7879</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="4" t="str">
+      <c r="D31" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F31" s="16">
+      <c r="E31" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" s="24">
         <v>6540</v>
       </c>
-      <c r="G31" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G31" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="21">
+        <v>8592</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>8592</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F32" s="16">
+      <c r="E32" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="24">
         <v>5996</v>
       </c>
-      <c r="G32" s="5" t="str">
+      <c r="G32" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33" s="21">
         <v>8656</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="4" t="str">
+      <c r="D33" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F33" s="16">
+      <c r="E33" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="24">
         <v>4045</v>
       </c>
-      <c r="G33" s="5" t="str">
+      <c r="G33" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34" s="21">
         <v>7421</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F34" s="16">
+      <c r="E34" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F34" s="24">
         <v>6540</v>
       </c>
-      <c r="G34" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G34" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="21">
+        <v>4785</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>4785</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="4" t="str">
+      <c r="E35" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="21">
+        <v>8628</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F35" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G35" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>8628</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F36" s="16">
+      <c r="E36" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="24">
         <v>5996</v>
       </c>
-      <c r="G36" s="5" t="str">
+      <c r="G36" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37" s="21">
         <v>8597</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="4" t="str">
+      <c r="D37" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F37" s="16">
+      <c r="E37" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F37" s="24">
         <v>5996</v>
       </c>
-      <c r="G37" s="5" t="str">
+      <c r="G37" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38" s="21">
         <v>8282</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F38" s="16">
+      <c r="E38" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="24">
         <v>5996</v>
       </c>
-      <c r="G38" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G38" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="21">
+        <v>8497</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="21">
+        <v>6039</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>8497</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D39" s="4" t="str">
+      <c r="E40" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="21">
+        <v>8528</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F41" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="21">
+        <v>8435</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G39" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="E42" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="21">
+        <v>8225</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>6039</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D40" s="4" t="str">
+      <c r="E43" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G43" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="21">
+        <v>8443</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G44" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="21">
+        <v>7526</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F40" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G40" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="E45" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="21">
+        <v>8664</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>8528</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F41" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G41" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>8435</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F42" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G42" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>8225</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F43" s="16">
+      <c r="E46" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="24">
         <v>6540</v>
       </c>
-      <c r="G43" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
-        <v>8443</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F44" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G44" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>7526</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G45" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
-        <v>8664</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F46" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G46" s="5" t="str">
+      <c r="G46" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47" s="21">
         <v>6259</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="4" t="str">
+      <c r="D47" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F47" s="16">
+      <c r="E47" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="24">
         <v>6540</v>
       </c>
-      <c r="G47" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G47" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="21">
+        <v>7108</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D48" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="21">
+        <v>7934</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
-        <v>7108</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D48" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F48" s="16">
+      <c r="E49" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49" s="24">
         <v>5996</v>
       </c>
-      <c r="G48" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G49" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="21">
+        <v>8283</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
-        <v>7934</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" s="4" t="str">
+      <c r="E50" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="21">
+        <v>8370</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F49" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G49" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
-        <v>8283</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F50" s="16">
+      <c r="E51" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51" s="24">
         <v>4045</v>
       </c>
-      <c r="G50" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>8370</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D51" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F51" s="16">
+      <c r="G51" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="21">
+        <v>8561</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F52" s="24">
         <v>4045</v>
       </c>
-      <c r="G51" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>8561</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F52" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G52" s="5" t="str">
+      <c r="G52" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53" s="21">
         <v>7694</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="4" t="str">
+      <c r="D53" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F53" s="16">
+      <c r="E53" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F53" s="24">
         <v>5996</v>
       </c>
-      <c r="G53" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Não</v>
+      <c r="G53" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54" s="21">
         <v>8662</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="4" t="str">
+      <c r="D54" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F54" s="16">
+      <c r="E54" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="24">
         <v>5996</v>
       </c>
-      <c r="G54" s="5" t="str">
+      <c r="G54" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55" s="21">
         <v>8190</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4" t="str">
+      <c r="D55" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F55" s="16">
+      <c r="E55" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" s="24">
         <v>4045</v>
       </c>
-      <c r="G55" s="5" t="str">
+      <c r="G55" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+      <c r="A56" s="21">
         <v>8301</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4" t="str">
+      <c r="D56" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F56" s="16">
+      <c r="E56" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F56" s="24">
         <v>6540</v>
       </c>
-      <c r="G56" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G56" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="21">
+        <v>4227</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
-        <v>4227</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D57" s="4" t="str">
+      <c r="E57" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F57" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="21">
+        <v>8428</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D58" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F57" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G57" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>8428</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D58" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F58" s="16">
+      <c r="E58" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F58" s="24">
         <v>5996</v>
       </c>
-      <c r="G58" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G58" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
+      <c r="A59" s="21">
         <v>8655</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="D59" s="4" t="str">
+      <c r="D59" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F59" s="16">
+      <c r="E59" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F59" s="24">
         <v>5996</v>
       </c>
-      <c r="G59" s="5" t="str">
+      <c r="G59" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
+      <c r="A60" s="21">
         <v>8060</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="D60" s="4" t="str">
+      <c r="D60" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>-</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F60" s="16">
+      <c r="E60" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F60" s="24">
         <v>4045</v>
       </c>
-      <c r="G60" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
+      <c r="G60" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="21">
+        <v>7429</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F61" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="21">
+        <v>6927</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D62" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F62" s="24">
+        <v>4045</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="21">
+        <v>8394</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D63" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F63" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G63" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="21">
+        <v>8491</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D64" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F64" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="21">
+        <v>8373</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D65" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Sim</v>
+      </c>
+      <c r="E65" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F65" s="24">
+        <v>6540</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="21">
+        <v>8503</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D66" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
-        <v>7429</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D61" s="4" t="str">
+      <c r="E66" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F66" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="21">
+        <v>6588</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="21">
+        <v>8203</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F61" s="16">
+      <c r="E68" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F68" s="24">
         <v>4045</v>
       </c>
-      <c r="G61" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>6927</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D62" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F62" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G62" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
-        <v>8394</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D63" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F63" s="16">
+      <c r="G68" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="21">
+        <v>8501</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F69" s="24">
+        <v>5996</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="21">
+        <v>8562</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="24" t="str">
+        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
+        <v>Não</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F70" s="24">
         <v>6540</v>
       </c>
-      <c r="G63" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
-        <v>8491</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D64" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F64" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G64" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
-        <v>8373</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D65" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F65" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G65" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
-        <v>8503</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D66" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G66" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Não</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
-        <v>6588</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D67" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F67" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G67" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
-        <v>8203</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F68" s="16">
-        <v>4045</v>
-      </c>
-      <c r="G68" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Não</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
-        <v>8501</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F69" s="16">
-        <v>5996</v>
-      </c>
-      <c r="G69" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="7">
-        <v>8562</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D70" s="4" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
-        <v>Não</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F70" s="16">
-        <v>6540</v>
-      </c>
-      <c r="G70" s="5" t="str">
+      <c r="G70" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="7">
+      <c r="A71" s="21">
         <v>8339</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="D71" s="4" t="str">
+      <c r="D71" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Sim</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F71" s="16">
+      <c r="E71" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F71" s="24">
         <v>4045</v>
       </c>
-      <c r="G71" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G71" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="12">
+      <c r="A72" s="21">
         <v>7140</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="D72" s="15" t="str">
+      <c r="D72" s="24" t="str">
         <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Tabela5[#All],2,0),"-")</f>
         <v>Não</v>
       </c>
-      <c r="E72" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="F72" s="16">
+      <c r="E72" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F72" s="24">
         <v>5996</v>
       </c>
-      <c r="G72" s="5" t="str">
-        <f>IFERROR(VLOOKUP(Tabela1[[#This Row],[login]],Certificados!A:B,2,0),"-")</f>
-        <v>Sim</v>
+      <c r="G72" s="24" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A8">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B72">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B70">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C70">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
@@ -3845,1333 +3663,1333 @@
   <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="5"/>
-    <col min="5" max="5" width="23.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="3"/>
+    <col min="5" max="5" width="23.5703125" style="3" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C1"/>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="17" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G3" t="s">
         <v>164</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G6" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G7" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G8" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G9" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G13" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G16" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G17" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
         <v>184</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G18" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G19" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G20" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
         <v>82</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G21" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G22" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G23" t="s">
         <v>81</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G24" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G25" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
         <v>166</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G27" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G28" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G30" t="s">
         <v>51</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G31" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G32" t="s">
         <v>70</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G33" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="s">
         <v>38</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G35" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
         <v>185</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G38" t="s">
         <v>30</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G39" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C40"/>
       <c r="D40" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G40" t="s">
         <v>53</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C41"/>
       <c r="D41" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G41" t="s">
         <v>165</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C42"/>
       <c r="D42" t="s">
         <v>68</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G42" t="s">
         <v>57</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C43"/>
       <c r="D43" t="s">
         <v>70</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G43" t="s">
         <v>60</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C44"/>
       <c r="D44" t="s">
         <v>79</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G44" t="s">
         <v>68</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C45"/>
       <c r="D45" t="s">
         <v>80</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G45" t="s">
         <v>69</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C46"/>
       <c r="D46" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G46" t="s">
         <v>166</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C47"/>
       <c r="D47" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G47" t="s">
         <v>73</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C48"/>
       <c r="D48" t="s">
         <v>37</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G48" t="s">
         <v>79</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H48" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C49"/>
       <c r="D49" t="s">
         <v>50</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G49" t="s">
         <v>86</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C50"/>
       <c r="D50" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G50" t="s">
         <v>89</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C51"/>
       <c r="D51" t="s">
         <v>71</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G51" t="s">
         <v>22</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C52"/>
       <c r="D52" t="s">
         <v>167</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G52" t="s">
         <v>39</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H52" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C53"/>
       <c r="D53" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G53" t="s">
         <v>43</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G54" t="s">
         <v>45</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C55"/>
       <c r="D55" t="s">
         <v>29</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G55" t="s">
         <v>48</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H55" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C56"/>
       <c r="D56" t="s">
         <v>32</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G56" t="s">
         <v>55</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H56" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C57"/>
       <c r="D57" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G57" t="s">
         <v>59</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H57" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C58"/>
       <c r="D58" t="s">
         <v>55</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G58" t="s">
         <v>71</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H58" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C59"/>
       <c r="D59" t="s">
         <v>57</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G59" t="s">
         <v>77</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H59" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C60"/>
       <c r="D60" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G60" t="s">
         <v>84</v>
       </c>
-      <c r="H60" s="5" t="s">
+      <c r="H60" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C61"/>
       <c r="D61" t="s">
         <v>66</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G61" t="s">
         <v>85</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="H61" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C62"/>
       <c r="D62" t="s">
         <v>67</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G62" t="s">
         <v>87</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="H62" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C63"/>
       <c r="D63" t="s">
         <v>76</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G63" t="s">
         <v>90</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H63" s="3" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5179,13 +4997,13 @@
       <c r="D64" t="s">
         <v>84</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G64" t="s">
         <v>21</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H64" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5193,13 +5011,13 @@
       <c r="D65" t="s">
         <v>85</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G65" t="s">
         <v>29</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="H65" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5207,13 +5025,13 @@
       <c r="D66" t="s">
         <v>87</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G66" t="s">
         <v>32</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="H66" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5221,13 +5039,13 @@
       <c r="D67" t="s">
         <v>90</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G67" t="s">
         <v>42</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H67" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5235,7 +5053,7 @@
       <c r="G68" t="s">
         <v>54</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="H68" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5243,7 +5061,7 @@
       <c r="G69" t="s">
         <v>56</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5251,7 +5069,7 @@
       <c r="G70" t="s">
         <v>67</v>
       </c>
-      <c r="H70" s="5" t="s">
+      <c r="H70" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5259,7 +5077,7 @@
       <c r="G71" t="s">
         <v>167</v>
       </c>
-      <c r="H71" s="5" t="s">
+      <c r="H71" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5267,7 +5085,7 @@
       <c r="G72" t="s">
         <v>72</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="H72" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5275,7 +5093,7 @@
       <c r="G73" t="s">
         <v>76</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="H73" s="3" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5283,7 +5101,7 @@
       <c r="G74" t="s">
         <v>80</v>
       </c>
-      <c r="H74" s="5" t="s">
+      <c r="H74" s="3" t="s">
         <v>169</v>
       </c>
     </row>
